--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -7,56 +7,131 @@
 </workbook>
 </file>
 
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0B1D3D"/>
+      <name val="Inter"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Inter"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0A2D5A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="1">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="18" customWidth="1"/>
+    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="8" max="8" width="18" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="18" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>indicator_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>indicator_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>value_buy</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>value_sell</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>currency</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>frequency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>source</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_url</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>fetched_at</t>
         </is>
@@ -83,32 +158,42 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>CNY</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>VES por unidad de moneda extranjera</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:35:29Z</t>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>2026-06-26T17:47:00Z</t>
         </is>
       </c>
     </row>
@@ -133,32 +218,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>EUR</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>VES por unidad de moneda extranjera</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:35:29Z</t>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>2026-06-26T17:47:00Z</t>
         </is>
       </c>
     </row>
@@ -183,32 +278,42 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>RUB</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>VES por unidad de moneda extranjera</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:35:29Z</t>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>2026-06-26T17:47:00Z</t>
         </is>
       </c>
     </row>
@@ -233,32 +338,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>TRY</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>VES por unidad de moneda extranjera</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:35:29Z</t>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>2026-06-26T17:47:00Z</t>
         </is>
       </c>
     </row>
@@ -283,32 +398,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>VES por unidad de moneda extranjera</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>daily</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Banco Central de Venezuela</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>2026-06-26T09:35:29Z</t>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>2026-06-26T17:47:00Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -437,6 +437,306 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>100.9793608</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-07-07T22:56:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>783.7787073</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-07-07T22:56:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>8.97360936</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-07-07T22:56:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>14.64594213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-07-07T22:56:56Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>685.9427</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-07-07T22:56:56Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -437,6 +437,306 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>100.9793608</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2026-07-08T07:42:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>783.7787073</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>2026-07-08T07:42:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>8.97360936</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>2026-07-08T07:42:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>14.64594213</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>2026-07-08T07:42:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>685.9427</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-07-08T07:42:32Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -737,6 +737,306 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>102.97425</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-07-08T21:39:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>798.29139724</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-07-08T21:39:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>9.1184853</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-07-08T21:39:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>14.94498596</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-07-08T21:39:38Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>700.2249</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-07-08T21:39:38Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -793,7 +793,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2026-07-08T21:39:38Z</t>
+          <t>2026-07-09T21:55:44Z</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2026-07-08T21:39:38Z</t>
+          <t>2026-07-09T21:55:44Z</t>
         </is>
       </c>
     </row>
@@ -913,7 +913,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2026-07-08T21:39:38Z</t>
+          <t>2026-07-09T21:55:44Z</t>
         </is>
       </c>
     </row>
@@ -973,7 +973,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2026-07-08T21:39:38Z</t>
+          <t>2026-07-09T21:55:44Z</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2026-07-08T21:39:38Z</t>
+          <t>2026-07-09T21:55:44Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1037,6 +1037,306 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>104.46501118</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:34:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>811.44935403</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:34:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>9.32090228</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:34:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>15.16763197</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:34:03Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-07-10</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>709.6935</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2026-07-10T21:34:03Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1337,6 +1337,306 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>106.45439116</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>823.94258468</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>9.36848968</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>15.35294972</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>721.3456</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>2026-07-11T21:13:42Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-11T21:13:42Z</t>
+          <t>2026-07-12T21:14:53Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-11T21:13:42Z</t>
+          <t>2026-07-12T21:14:53Z</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-11T21:13:42Z</t>
+          <t>2026-07-12T21:14:53Z</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-11T21:13:42Z</t>
+          <t>2026-07-12T21:14:53Z</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-11T21:13:42Z</t>
+          <t>2026-07-12T21:14:53Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1393,7 +1393,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2026-07-12T21:14:53Z</t>
+          <t>2026-07-13T21:27:58Z</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2026-07-12T21:14:53Z</t>
+          <t>2026-07-13T21:27:58Z</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>2026-07-12T21:14:53Z</t>
+          <t>2026-07-13T21:27:58Z</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2026-07-12T21:14:53Z</t>
+          <t>2026-07-13T21:27:58Z</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2026-07-12T21:14:53Z</t>
+          <t>2026-07-13T21:27:58Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1637,6 +1637,306 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>106.80026552</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:30:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>825.49641981</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:30:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>9.44024732</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:30:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>15.40511573</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:30:48Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>723.999</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>2026-07-14T21:30:48Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>
--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1650,11 +1650,11 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D27">
-        <v>106.80026552</v>
+        <v>107.20836103</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>2026-07-14T21:30:48Z</t>
+          <t>2026-07-15T08:47:15Z</t>
         </is>
       </c>
     </row>
@@ -1710,11 +1710,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D28">
-        <v>825.49641981</v>
+        <v>830.63195644</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2026-07-14T21:30:48Z</t>
+          <t>2026-07-15T08:47:15Z</t>
         </is>
       </c>
     </row>
@@ -1770,11 +1770,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D29">
-        <v>9.44024732</v>
+        <v>9.35929659</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>2026-07-14T21:30:48Z</t>
+          <t>2026-07-15T08:47:15Z</t>
         </is>
       </c>
     </row>
@@ -1830,11 +1830,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D30">
-        <v>15.40511573</v>
+        <v>15.43121466</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>2026-07-14T21:30:48Z</t>
+          <t>2026-07-15T08:47:15Z</t>
         </is>
       </c>
     </row>
@@ -1890,11 +1890,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="D31">
-        <v>723.999</v>
+        <v>725.747</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>2026-07-14T21:30:48Z</t>
+          <t>2026-07-15T08:47:15Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -16,7 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-es-ES]#,##0.00"/>
+  </numFmts>
   <fonts count="4">
     <font>
       <name val="Calibri"/>
@@ -64,7 +66,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -72,6 +74,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -105,6 +110,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -513,7 +521,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>91.54102484000001</v>
       </c>
       <c r="E7" s="4" t="n"/>
@@ -565,7 +573,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>708.39006975</v>
       </c>
       <c r="E8" s="4" t="n"/>
@@ -617,7 +625,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>8.20429193</v>
       </c>
       <c r="E9" s="4" t="n"/>
@@ -669,7 +677,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>13.37808724</v>
       </c>
       <c r="E10" s="4" t="n"/>
@@ -721,7 +729,7 @@
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>622.2135</v>
       </c>
       <c r="E11" s="4" t="n"/>
@@ -773,7 +781,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>100.9793608</v>
       </c>
       <c r="E12" s="4" t="n"/>
@@ -825,7 +833,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>783.7787073</v>
       </c>
       <c r="E13" s="4" t="n"/>
@@ -877,7 +885,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>8.973609359999999</v>
       </c>
       <c r="E14" s="4" t="n"/>
@@ -929,7 +937,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <v>14.64594213</v>
       </c>
       <c r="E15" s="4" t="n"/>
@@ -981,7 +989,7 @@
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>685.9426999999999</v>
       </c>
       <c r="E16" s="4" t="n"/>
@@ -1033,7 +1041,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>102.97425</v>
       </c>
       <c r="E17" s="4" t="n"/>
@@ -1085,7 +1093,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>798.29139724</v>
       </c>
       <c r="E18" s="4" t="n"/>
@@ -1137,7 +1145,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>9.1184853</v>
       </c>
       <c r="E19" s="4" t="n"/>
@@ -1189,7 +1197,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>14.94498596</v>
       </c>
       <c r="E20" s="4" t="n"/>
@@ -1241,7 +1249,7 @@
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>700.2249</v>
       </c>
       <c r="E21" s="4" t="n"/>
@@ -1293,7 +1301,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>104.46501118</v>
       </c>
       <c r="E22" s="4" t="n"/>
@@ -1345,7 +1353,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>811.44935403</v>
       </c>
       <c r="E23" s="4" t="n"/>
@@ -1397,7 +1405,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>9.32090228</v>
       </c>
       <c r="E24" s="4" t="n"/>
@@ -1449,7 +1457,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>15.16763197</v>
       </c>
       <c r="E25" s="4" t="n"/>
@@ -1501,7 +1509,7 @@
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>709.6935</v>
       </c>
       <c r="E26" s="4" t="n"/>
@@ -1553,7 +1561,7 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="5" t="n">
         <v>106.45439116</v>
       </c>
       <c r="E27" s="4" t="n"/>
@@ -1605,7 +1613,7 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="5" t="n">
         <v>823.94258468</v>
       </c>
       <c r="E28" s="4" t="n"/>
@@ -1657,7 +1665,7 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>9.36848968</v>
       </c>
       <c r="E29" s="4" t="n"/>
@@ -1709,7 +1717,7 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="5" t="n">
         <v>15.35294972</v>
       </c>
       <c r="E30" s="4" t="n"/>
@@ -1761,7 +1769,7 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="5" t="n">
         <v>721.3456</v>
       </c>
       <c r="E31" s="4" t="n"/>
@@ -1813,7 +1821,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="5" t="n">
         <v>107.20836103</v>
       </c>
       <c r="E32" s="4" t="n"/>
@@ -1865,7 +1873,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="5" t="n">
         <v>830.63195644</v>
       </c>
       <c r="E33" s="4" t="n"/>
@@ -1917,7 +1925,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="5" t="n">
         <v>9.35929659</v>
       </c>
       <c r="E34" s="4" t="n"/>
@@ -1969,7 +1977,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>15.43121466</v>
       </c>
       <c r="E35" s="4" t="n"/>
@@ -2021,7 +2029,7 @@
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="5" t="n">
         <v>725.747</v>
       </c>
       <c r="E36" s="4" t="n"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -446,62 +446,62 @@
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>indicator_id</t>
+          <t>ID indicador</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>indicator_name</t>
+          <t>Indicador</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>Fecha</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>Valor</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>value_buy</t>
+          <t>Valor compra</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>value_sell</t>
+          <t>Valor venta</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>currency</t>
+          <t>Moneda</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>Unidad</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>frequency</t>
+          <t>Frecuencia</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>source</t>
+          <t>Fuente</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>source_url</t>
+          <t>URL fuente</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>fetched_at</t>
+          <t>Fecha de captura</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="serie_historica" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="serie_historica" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -84,11 +84,79 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
@@ -103,16 +171,13 @@
         <cNvPicPr/>
       </nvPicPr>
       <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+        <a:prstGeom prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -409,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2130,266 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>107.46169527</v>
+      </c>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:29:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n">
+        <v>832.2478198699999</v>
+      </c>
+      <c r="E38" s="4" t="n"/>
+      <c r="F38" s="4" t="n"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:29:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n">
+        <v>9.3623063</v>
+      </c>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:29:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>15.46781532</v>
+      </c>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:29:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>727.4512</v>
+      </c>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-15T21:29:02Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -2178,7 +2178,7 @@
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T21:29:02Z</t>
+          <t>2026-07-16T21:31:35Z</t>
         </is>
       </c>
     </row>
@@ -2230,7 +2230,7 @@
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T21:29:02Z</t>
+          <t>2026-07-16T21:31:35Z</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T21:29:02Z</t>
+          <t>2026-07-16T21:31:35Z</t>
         </is>
       </c>
     </row>
@@ -2334,7 +2334,7 @@
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T21:29:02Z</t>
+          <t>2026-07-16T21:31:35Z</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>2026-07-15T21:29:02Z</t>
+          <t>2026-07-16T21:31:35Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L41"/>
+  <dimension ref="A1:L46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2390,6 +2390,266 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>108.72438772</v>
+      </c>
+      <c r="E42" s="4" t="n"/>
+      <c r="F42" s="4" t="n"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18T21:13:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>843.19976838</v>
+      </c>
+      <c r="E43" s="4" t="n"/>
+      <c r="F43" s="4" t="n"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18T21:13:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>9.40358925</v>
+      </c>
+      <c r="E44" s="4" t="n"/>
+      <c r="F44" s="4" t="n"/>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18T21:13:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>15.6262158</v>
+      </c>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18T21:13:19Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>736.9339</v>
+      </c>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-18T21:13:19Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18T21:13:19Z</t>
+          <t>2026-07-19T21:21:55Z</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18T21:13:19Z</t>
+          <t>2026-07-19T21:21:55Z</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18T21:13:19Z</t>
+          <t>2026-07-19T21:21:55Z</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18T21:13:19Z</t>
+          <t>2026-07-19T21:21:55Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-18T21:13:19Z</t>
+          <t>2026-07-19T21:21:55Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -2438,7 +2438,7 @@
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19T21:21:55Z</t>
+          <t>2026-07-20T21:40:27Z</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19T21:21:55Z</t>
+          <t>2026-07-20T21:40:27Z</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19T21:21:55Z</t>
+          <t>2026-07-20T21:40:27Z</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19T21:21:55Z</t>
+          <t>2026-07-20T21:40:27Z</t>
         </is>
       </c>
     </row>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>2026-07-19T21:21:55Z</t>
+          <t>2026-07-20T21:40:27Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L46"/>
+  <dimension ref="A1:L51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2650,6 +2650,266 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n">
+        <v>108.97578749</v>
+      </c>
+      <c r="E47" s="4" t="n"/>
+      <c r="F47" s="4" t="n"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:38:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>840.85744397</v>
+      </c>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L48" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:38:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>9.362866390000001</v>
+      </c>
+      <c r="E49" s="4" t="n"/>
+      <c r="F49" s="4" t="n"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:38:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="n">
+        <v>15.61995292</v>
+      </c>
+      <c r="E50" s="4" t="n"/>
+      <c r="F50" s="4" t="n"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:38:11Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="n">
+        <v>737.2320999999999</v>
+      </c>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-21T21:38:11Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2910,6 +2910,266 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>108.96066154</v>
+      </c>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:35:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="n">
+        <v>841.84173862</v>
+      </c>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:35:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="n">
+        <v>9.394368330000001</v>
+      </c>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I54" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:35:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="n">
+        <v>15.62987267</v>
+      </c>
+      <c r="E55" s="4" t="n"/>
+      <c r="F55" s="4" t="n"/>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H55" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I55" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:35:32Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="n">
+        <v>737.8816</v>
+      </c>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H56" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I56" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-22T21:35:32Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -2958,7 +2958,7 @@
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:32Z</t>
+          <t>2026-07-23T21:34:39Z</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:32Z</t>
+          <t>2026-07-23T21:34:39Z</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:32Z</t>
+          <t>2026-07-23T21:34:39Z</t>
         </is>
       </c>
     </row>
@@ -3114,7 +3114,7 @@
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:32Z</t>
+          <t>2026-07-23T21:34:39Z</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>2026-07-22T21:35:32Z</t>
+          <t>2026-07-23T21:34:39Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L56"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3170,6 +3170,266 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="n">
+        <v>109.64637407</v>
+      </c>
+      <c r="E57" s="4" t="n"/>
+      <c r="F57" s="4" t="n"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I57" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:35:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="n">
+        <v>844.21891437</v>
+      </c>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I58" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:35:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>9.48111643</v>
+      </c>
+      <c r="E59" s="4" t="n"/>
+      <c r="F59" s="4" t="n"/>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I59" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:35:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="n">
+        <v>15.71369262</v>
+      </c>
+      <c r="E60" s="4" t="n"/>
+      <c r="F60" s="4" t="n"/>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I60" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:35:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="n">
+        <v>742.2292</v>
+      </c>
+      <c r="E61" s="4" t="n"/>
+      <c r="F61" s="4" t="n"/>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H61" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I61" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L61" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-24T21:35:40Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:35:40Z</t>
+          <t>2026-07-25T21:23:29Z</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:35:40Z</t>
+          <t>2026-07-25T21:23:29Z</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:35:40Z</t>
+          <t>2026-07-25T21:23:29Z</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:35:40Z</t>
+          <t>2026-07-25T21:23:29Z</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-24T21:35:40Z</t>
+          <t>2026-07-25T21:23:29Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:29Z</t>
+          <t>2026-07-26T21:25:18Z</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:29Z</t>
+          <t>2026-07-26T21:25:18Z</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:29Z</t>
+          <t>2026-07-26T21:25:18Z</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:29Z</t>
+          <t>2026-07-26T21:25:18Z</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-25T21:23:29Z</t>
+          <t>2026-07-26T21:25:18Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3218,7 +3218,7 @@
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:18Z</t>
+          <t>2026-07-27T21:37:10Z</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:18Z</t>
+          <t>2026-07-27T21:37:10Z</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:18Z</t>
+          <t>2026-07-27T21:37:10Z</t>
         </is>
       </c>
     </row>
@@ -3374,7 +3374,7 @@
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:18Z</t>
+          <t>2026-07-27T21:37:10Z</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26T21:25:18Z</t>
+          <t>2026-07-27T21:37:10Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3430,6 +3430,266 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="n">
+        <v>109.79874948</v>
+      </c>
+      <c r="E62" s="4" t="n"/>
+      <c r="F62" s="4" t="n"/>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H62" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I62" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="n">
+        <v>844.7538130200001</v>
+      </c>
+      <c r="E63" s="4" t="n"/>
+      <c r="F63" s="4" t="n"/>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K63" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L63" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="n">
+        <v>9.52039203</v>
+      </c>
+      <c r="E64" s="4" t="n"/>
+      <c r="F64" s="4" t="n"/>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H64" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I64" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>15.7042389</v>
+      </c>
+      <c r="E65" s="4" t="n"/>
+      <c r="F65" s="4" t="n"/>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:02Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>742.8105</v>
+      </c>
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-28T21:37:02Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L66"/>
+  <dimension ref="A1:L71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3690,6 +3690,266 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>110.21004788</v>
+      </c>
+      <c r="E67" s="4" t="n"/>
+      <c r="F67" s="4" t="n"/>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="n">
+        <v>848.82581826</v>
+      </c>
+      <c r="E68" s="4" t="n"/>
+      <c r="F68" s="4" t="n"/>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D69" s="5" t="n">
+        <v>9.29716273</v>
+      </c>
+      <c r="E69" s="4" t="n"/>
+      <c r="F69" s="4" t="n"/>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D70" s="5" t="n">
+        <v>15.73167976</v>
+      </c>
+      <c r="E70" s="4" t="n"/>
+      <c r="F70" s="4" t="n"/>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="n">
+        <v>745.6371</v>
+      </c>
+      <c r="E71" s="4" t="n"/>
+      <c r="F71" s="4" t="n"/>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-29T21:25:58Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3738,7 +3738,7 @@
       </c>
       <c r="L67" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:25:58Z</t>
+          <t>2026-07-30T21:40:37Z</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="L68" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:25:58Z</t>
+          <t>2026-07-30T21:40:37Z</t>
         </is>
       </c>
     </row>
@@ -3842,7 +3842,7 @@
       </c>
       <c r="L69" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:25:58Z</t>
+          <t>2026-07-30T21:40:37Z</t>
         </is>
       </c>
     </row>
@@ -3894,7 +3894,7 @@
       </c>
       <c r="L70" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:25:58Z</t>
+          <t>2026-07-30T21:40:37Z</t>
         </is>
       </c>
     </row>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
-          <t>2026-07-29T21:25:58Z</t>
+          <t>2026-07-30T21:40:37Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L71"/>
+  <dimension ref="A1:L76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3950,6 +3950,266 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="n">
+        <v>110.9247452</v>
+      </c>
+      <c r="E72" s="4" t="n"/>
+      <c r="F72" s="4" t="n"/>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="n">
+        <v>861.1867265</v>
+      </c>
+      <c r="E73" s="4" t="n"/>
+      <c r="F73" s="4" t="n"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>9.44969661</v>
+      </c>
+      <c r="E74" s="4" t="n"/>
+      <c r="F74" s="4" t="n"/>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="n">
+        <v>15.75728956</v>
+      </c>
+      <c r="E75" s="4" t="n"/>
+      <c r="F75" s="4" t="n"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:24Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>748.7864</v>
+      </c>
+      <c r="E76" s="4" t="n"/>
+      <c r="F76" s="4" t="n"/>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:36:24Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3998,7 +3998,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:24Z</t>
+          <t>2026-08-01T21:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:24Z</t>
+          <t>2026-08-01T21:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:24Z</t>
+          <t>2026-08-01T21:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:24Z</t>
+          <t>2026-08-01T21:23:40Z</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-31T21:36:24Z</t>
+          <t>2026-08-01T21:23:40Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3998,7 +3998,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:40Z</t>
+          <t>2026-08-02T21:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:40Z</t>
+          <t>2026-08-02T21:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:40Z</t>
+          <t>2026-08-02T21:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:40Z</t>
+          <t>2026-08-02T21:23:38Z</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-01T21:23:40Z</t>
+          <t>2026-08-02T21:23:38Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -3998,7 +3998,7 @@
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:38Z</t>
+          <t>2026-08-03T21:38:34Z</t>
         </is>
       </c>
     </row>
@@ -4050,7 +4050,7 @@
       </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:38Z</t>
+          <t>2026-08-03T21:38:34Z</t>
         </is>
       </c>
     </row>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="L74" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:38Z</t>
+          <t>2026-08-03T21:38:34Z</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4154,7 @@
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:38Z</t>
+          <t>2026-08-03T21:38:34Z</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
-          <t>2026-08-02T21:23:38Z</t>
+          <t>2026-08-03T21:38:34Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L76"/>
+  <dimension ref="A1:L81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4210,6 +4210,266 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>111.83011239</v>
+      </c>
+      <c r="E77" s="4" t="n"/>
+      <c r="F77" s="4" t="n"/>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>870.04451212</v>
+      </c>
+      <c r="E78" s="4" t="n"/>
+      <c r="F78" s="4" t="n"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D79" s="5" t="n">
+        <v>9.28964448</v>
+      </c>
+      <c r="E79" s="4" t="n"/>
+      <c r="F79" s="4" t="n"/>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H79" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I79" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L79" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
+        <v>15.88452744</v>
+      </c>
+      <c r="E80" s="4" t="n"/>
+      <c r="F80" s="4" t="n"/>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H80" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I80" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L80" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:37Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="n">
+        <v>755.1552</v>
+      </c>
+      <c r="E81" s="4" t="n"/>
+      <c r="F81" s="4" t="n"/>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H81" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I81" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L81" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-04T21:47:37Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -4258,7 +4258,7 @@
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:37Z</t>
+          <t>2026-08-05T21:44:02Z</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:37Z</t>
+          <t>2026-08-05T21:44:02Z</t>
         </is>
       </c>
     </row>
@@ -4362,7 +4362,7 @@
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:37Z</t>
+          <t>2026-08-05T21:44:02Z</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="L80" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:37Z</t>
+          <t>2026-08-05T21:44:02Z</t>
         </is>
       </c>
     </row>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="L81" s="4" t="inlineStr">
         <is>
-          <t>2026-08-04T21:47:37Z</t>
+          <t>2026-08-05T21:44:02Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L81"/>
+  <dimension ref="A1:L86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4470,6 +4470,266 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D82" s="5" t="n">
+        <v>112.13317428</v>
+      </c>
+      <c r="E82" s="4" t="n"/>
+      <c r="F82" s="4" t="n"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H82" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I82" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L82" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>871.89443742</v>
+      </c>
+      <c r="E83" s="4" t="n"/>
+      <c r="F83" s="4" t="n"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L83" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D84" s="5" t="n">
+        <v>9.302547690000001</v>
+      </c>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H84" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I84" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L84" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D85" s="5" t="n">
+        <v>15.89903686</v>
+      </c>
+      <c r="E85" s="4" t="n"/>
+      <c r="F85" s="4" t="n"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H85" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I85" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L85" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:40Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="D86" s="5" t="n">
+        <v>756.7083</v>
+      </c>
+      <c r="E86" s="4" t="n"/>
+      <c r="F86" s="4" t="n"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H86" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I86" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L86" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-07T00:56:40Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -4518,7 +4518,7 @@
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:40Z</t>
+          <t>2026-08-07T21:08:51Z</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:40Z</t>
+          <t>2026-08-07T21:08:51Z</t>
         </is>
       </c>
     </row>
@@ -4622,7 +4622,7 @@
       </c>
       <c r="L84" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:40Z</t>
+          <t>2026-08-07T21:08:51Z</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:40Z</t>
+          <t>2026-08-07T21:08:51Z</t>
         </is>
       </c>
     </row>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>2026-08-07T00:56:40Z</t>
+          <t>2026-08-07T21:08:51Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4730,6 +4730,266 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="n">
+        <v>112.27980257</v>
+      </c>
+      <c r="E87" s="4" t="n"/>
+      <c r="F87" s="4" t="n"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H87" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I87" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L87" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="n">
+        <v>875.2169568</v>
+      </c>
+      <c r="E88" s="4" t="n"/>
+      <c r="F88" s="4" t="n"/>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H88" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I88" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L88" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="n">
+        <v>9.250709479999999</v>
+      </c>
+      <c r="E89" s="4" t="n"/>
+      <c r="F89" s="4" t="n"/>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L89" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="n">
+        <v>15.8805586</v>
+      </c>
+      <c r="E90" s="4" t="n"/>
+      <c r="F90" s="4" t="n"/>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I90" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K90" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L90" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="n">
+        <v>757.5406</v>
+      </c>
+      <c r="E91" s="4" t="n"/>
+      <c r="F91" s="4" t="n"/>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H91" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I91" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L91" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-08T20:57:33Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -4778,7 +4778,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:33Z</t>
+          <t>2026-08-09T21:01:45Z</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:33Z</t>
+          <t>2026-08-09T21:01:45Z</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:33Z</t>
+          <t>2026-08-09T21:01:45Z</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:33Z</t>
+          <t>2026-08-09T21:01:45Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-08T20:57:33Z</t>
+          <t>2026-08-09T21:01:45Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -4778,7 +4778,7 @@
       </c>
       <c r="L87" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:01:45Z</t>
+          <t>2026-08-10T21:10:49Z</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:01:45Z</t>
+          <t>2026-08-10T21:10:49Z</t>
         </is>
       </c>
     </row>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="L89" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:01:45Z</t>
+          <t>2026-08-10T21:10:49Z</t>
         </is>
       </c>
     </row>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="L90" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:01:45Z</t>
+          <t>2026-08-10T21:10:49Z</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4986,7 @@
       </c>
       <c r="L91" s="4" t="inlineStr">
         <is>
-          <t>2026-08-09T21:01:45Z</t>
+          <t>2026-08-10T21:10:49Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -4990,6 +4990,266 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="n">
+        <v>112.85811502</v>
+      </c>
+      <c r="E92" s="4" t="n"/>
+      <c r="F92" s="4" t="n"/>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H92" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I92" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L92" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="n">
+        <v>879.34991967</v>
+      </c>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I93" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L93" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="n">
+        <v>9.227987629999999</v>
+      </c>
+      <c r="E94" s="4" t="n"/>
+      <c r="F94" s="4" t="n"/>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I94" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L94" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D95" s="5" t="n">
+        <v>15.95383256</v>
+      </c>
+      <c r="E95" s="4" t="n"/>
+      <c r="F95" s="4" t="n"/>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H95" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I95" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L95" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:39Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="D96" s="5" t="n">
+        <v>761.2166999999999</v>
+      </c>
+      <c r="E96" s="4" t="n"/>
+      <c r="F96" s="4" t="n"/>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H96" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I96" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K96" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L96" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11T21:14:39Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:L101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5250,6 +5250,266 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D97" s="5" t="n">
+        <v>113.32917191</v>
+      </c>
+      <c r="E97" s="4" t="n"/>
+      <c r="F97" s="4" t="n"/>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I97" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L97" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D98" s="5" t="n">
+        <v>882.29523246</v>
+      </c>
+      <c r="E98" s="4" t="n"/>
+      <c r="F98" s="4" t="n"/>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I98" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L98" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D99" s="5" t="n">
+        <v>9.254735439999999</v>
+      </c>
+      <c r="E99" s="4" t="n"/>
+      <c r="F99" s="4" t="n"/>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I99" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L99" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D100" s="5" t="n">
+        <v>16.01233057</v>
+      </c>
+      <c r="E100" s="4" t="n"/>
+      <c r="F100" s="4" t="n"/>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H100" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I100" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L100" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D101" s="5" t="n">
+        <v>764.3486</v>
+      </c>
+      <c r="E101" s="4" t="n"/>
+      <c r="F101" s="4" t="n"/>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I101" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12T21:12:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L101"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5510,6 +5510,266 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D102" s="5" t="n">
+        <v>113.75555159</v>
+      </c>
+      <c r="E102" s="4" t="n"/>
+      <c r="F102" s="4" t="n"/>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I102" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K102" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="n">
+        <v>885.07948384</v>
+      </c>
+      <c r="E103" s="4" t="n"/>
+      <c r="F103" s="4" t="n"/>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I103" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="n">
+        <v>9.27391824</v>
+      </c>
+      <c r="E104" s="4" t="n"/>
+      <c r="F104" s="4" t="n"/>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H104" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I104" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="n">
+        <v>16.05902715</v>
+      </c>
+      <c r="E105" s="4" t="n"/>
+      <c r="F105" s="4" t="n"/>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H105" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I105" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:13Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D106" s="5" t="n">
+        <v>766.8603000000001</v>
+      </c>
+      <c r="E106" s="4" t="n"/>
+      <c r="F106" s="4" t="n"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H106" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I106" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-13T21:12:13Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L106"/>
+  <dimension ref="A1:L111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5770,6 +5770,266 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D107" s="5" t="n">
+        <v>114.60548294</v>
+      </c>
+      <c r="E107" s="4" t="n"/>
+      <c r="F107" s="4" t="n"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H107" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I107" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D108" s="5" t="n">
+        <v>894.49018618</v>
+      </c>
+      <c r="E108" s="4" t="n"/>
+      <c r="F108" s="4" t="n"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H108" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I108" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D109" s="5" t="n">
+        <v>9.170642559999999</v>
+      </c>
+      <c r="E109" s="4" t="n"/>
+      <c r="F109" s="4" t="n"/>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H109" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I109" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D110" s="5" t="n">
+        <v>16.13545447</v>
+      </c>
+      <c r="E110" s="4" t="n"/>
+      <c r="F110" s="4" t="n"/>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H110" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I110" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K110" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:52Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D111" s="5" t="n">
+        <v>772.5441</v>
+      </c>
+      <c r="E111" s="4" t="n"/>
+      <c r="F111" s="4" t="n"/>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H111" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I111" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-14T20:54:52Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:54:52Z</t>
+          <t>2026-08-15T20:46:49Z</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:54:52Z</t>
+          <t>2026-08-15T20:46:49Z</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:54:52Z</t>
+          <t>2026-08-15T20:46:49Z</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:54:52Z</t>
+          <t>2026-08-15T20:46:49Z</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-14T20:54:52Z</t>
+          <t>2026-08-15T20:46:49Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:46:49Z</t>
+          <t>2026-08-16T20:45:49Z</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:46:49Z</t>
+          <t>2026-08-16T20:45:49Z</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:46:49Z</t>
+          <t>2026-08-16T20:45:49Z</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:46:49Z</t>
+          <t>2026-08-16T20:45:49Z</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-15T20:46:49Z</t>
+          <t>2026-08-16T20:45:49Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -5818,7 +5818,7 @@
       </c>
       <c r="L107" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:45:49Z</t>
+          <t>2026-08-17T20:52:31Z</t>
         </is>
       </c>
     </row>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:45:49Z</t>
+          <t>2026-08-17T20:52:31Z</t>
         </is>
       </c>
     </row>
@@ -5922,7 +5922,7 @@
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:45:49Z</t>
+          <t>2026-08-17T20:52:31Z</t>
         </is>
       </c>
     </row>
@@ -5974,7 +5974,7 @@
       </c>
       <c r="L110" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:45:49Z</t>
+          <t>2026-08-17T20:52:31Z</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6026,7 @@
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>2026-08-16T20:45:49Z</t>
+          <t>2026-08-17T20:52:31Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L111"/>
+  <dimension ref="A1:L116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6030,6 +6030,266 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D112" s="5" t="n">
+        <v>116.01079858</v>
+      </c>
+      <c r="E112" s="4" t="n"/>
+      <c r="F112" s="4" t="n"/>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H112" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I112" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="n">
+        <v>911.21815526</v>
+      </c>
+      <c r="E113" s="4" t="n"/>
+      <c r="F113" s="4" t="n"/>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H113" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I113" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="n">
+        <v>9.313974200000001</v>
+      </c>
+      <c r="E114" s="4" t="n"/>
+      <c r="F114" s="4" t="n"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H114" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I114" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L114" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="n">
+        <v>16.26516767</v>
+      </c>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H115" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I115" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:06Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="n">
+        <v>779.9521999999999</v>
+      </c>
+      <c r="E116" s="4" t="n"/>
+      <c r="F116" s="4" t="n"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H116" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I116" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-21T16:34:06Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -6078,7 +6078,7 @@
       </c>
       <c r="L112" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:06Z</t>
+          <t>2026-08-21T20:49:17Z</t>
         </is>
       </c>
     </row>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:06Z</t>
+          <t>2026-08-21T20:49:17Z</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="L114" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:06Z</t>
+          <t>2026-08-21T20:49:17Z</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="L115" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:06Z</t>
+          <t>2026-08-21T20:49:17Z</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>2026-08-21T16:34:06Z</t>
+          <t>2026-08-21T20:49:17Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L116"/>
+  <dimension ref="A1:L121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6290,6 +6290,266 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="n">
+        <v>116.75668477</v>
+      </c>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H117" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I117" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="n">
+        <v>916.00808978</v>
+      </c>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H118" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I118" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="n">
+        <v>9.487185589999999</v>
+      </c>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H119" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I119" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J119" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="n">
+        <v>16.32674365</v>
+      </c>
+      <c r="E120" s="4" t="n"/>
+      <c r="F120" s="4" t="n"/>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H120" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I120" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J120" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:29Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="n">
+        <v>784.6633</v>
+      </c>
+      <c r="E121" s="4" t="n"/>
+      <c r="F121" s="4" t="n"/>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H121" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I121" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L121" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-22T20:47:29Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -6338,7 +6338,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:29Z</t>
+          <t>2026-08-23T20:47:13Z</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:29Z</t>
+          <t>2026-08-23T20:47:13Z</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:29Z</t>
+          <t>2026-08-23T20:47:13Z</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:29Z</t>
+          <t>2026-08-23T20:47:13Z</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-22T20:47:29Z</t>
+          <t>2026-08-23T20:47:13Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -6338,7 +6338,7 @@
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:13Z</t>
+          <t>2026-08-24T20:57:29Z</t>
         </is>
       </c>
     </row>
@@ -6390,7 +6390,7 @@
       </c>
       <c r="L118" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:13Z</t>
+          <t>2026-08-24T20:57:29Z</t>
         </is>
       </c>
     </row>
@@ -6442,7 +6442,7 @@
       </c>
       <c r="L119" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:13Z</t>
+          <t>2026-08-24T20:57:29Z</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:13Z</t>
+          <t>2026-08-24T20:57:29Z</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="L121" s="4" t="inlineStr">
         <is>
-          <t>2026-08-23T20:47:13Z</t>
+          <t>2026-08-24T20:57:29Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L121"/>
+  <dimension ref="A1:L126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6550,6 +6550,266 @@
         </is>
       </c>
     </row>
+    <row r="122">
+      <c r="A122" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="n">
+        <v>116.79971732</v>
+      </c>
+      <c r="E122" s="4" t="n"/>
+      <c r="F122" s="4" t="n"/>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H122" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I122" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L122" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="n">
+        <v>916.02670993</v>
+      </c>
+      <c r="E123" s="4" t="n"/>
+      <c r="F123" s="4" t="n"/>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H123" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I123" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J123" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L123" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="n">
+        <v>9.414429780000001</v>
+      </c>
+      <c r="E124" s="4" t="n"/>
+      <c r="F124" s="4" t="n"/>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H124" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I124" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J124" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L124" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="n">
+        <v>16.32999274</v>
+      </c>
+      <c r="E125" s="4" t="n"/>
+      <c r="F125" s="4" t="n"/>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H125" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I125" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J125" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L125" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:42Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="n">
+        <v>785.0693</v>
+      </c>
+      <c r="E126" s="4" t="n"/>
+      <c r="F126" s="4" t="n"/>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H126" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I126" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J126" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L126" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-25T20:54:42Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L126"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -6810,6 +6810,266 @@
         </is>
       </c>
     </row>
+    <row r="127">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="n">
+        <v>117.73038756</v>
+      </c>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H127" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I127" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J127" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L127" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="n">
+        <v>921.81425952</v>
+      </c>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H128" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I128" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L128" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="n">
+        <v>9.379186750000001</v>
+      </c>
+      <c r="E129" s="4" t="n"/>
+      <c r="F129" s="4" t="n"/>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H129" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I129" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L129" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="n">
+        <v>16.44680364</v>
+      </c>
+      <c r="E130" s="4" t="n"/>
+      <c r="F130" s="4" t="n"/>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H130" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L130" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:27Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="n">
+        <v>791.3248</v>
+      </c>
+      <c r="E131" s="4" t="n"/>
+      <c r="F131" s="4" t="n"/>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H131" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I131" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J131" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L131" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-26T23:55:27Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7070,6 +7070,266 @@
         </is>
       </c>
     </row>
+    <row r="132">
+      <c r="A132" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="n">
+        <v>117.81631073</v>
+      </c>
+      <c r="E132" s="4" t="n"/>
+      <c r="F132" s="4" t="n"/>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H132" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I132" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J132" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L132" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="n">
+        <v>921.88003881</v>
+      </c>
+      <c r="E133" s="4" t="n"/>
+      <c r="F133" s="4" t="n"/>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H133" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I133" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L133" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="n">
+        <v>9.174489510000001</v>
+      </c>
+      <c r="E134" s="4" t="n"/>
+      <c r="F134" s="4" t="n"/>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H134" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I134" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J134" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L134" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="n">
+        <v>16.44714131</v>
+      </c>
+      <c r="E135" s="4" t="n"/>
+      <c r="F135" s="4" t="n"/>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H135" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I135" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J135" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L135" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:47Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="n">
+        <v>791.6667</v>
+      </c>
+      <c r="E136" s="4" t="n"/>
+      <c r="F136" s="4" t="n"/>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H136" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I136" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J136" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L136" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-28T04:24:47Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L136"/>
+  <dimension ref="A1:L141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7330,6 +7330,266 @@
         </is>
       </c>
     </row>
+    <row r="137">
+      <c r="A137" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="n">
+        <v>118.23020181</v>
+      </c>
+      <c r="E137" s="4" t="n"/>
+      <c r="F137" s="4" t="n"/>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H137" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I137" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J137" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L137" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="n">
+        <v>922.69121677</v>
+      </c>
+      <c r="E138" s="4" t="n"/>
+      <c r="F138" s="4" t="n"/>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H138" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I138" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J138" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L138" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="n">
+        <v>9.22739438</v>
+      </c>
+      <c r="E139" s="4" t="n"/>
+      <c r="F139" s="4" t="n"/>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I139" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L139" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="n">
+        <v>16.47982495</v>
+      </c>
+      <c r="E140" s="4" t="n"/>
+      <c r="F140" s="4" t="n"/>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H140" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I140" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L140" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:33Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="n">
+        <v>794.9917</v>
+      </c>
+      <c r="E141" s="4" t="n"/>
+      <c r="F141" s="4" t="n"/>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L141" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-29T02:52:33Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:33Z</t>
+          <t>2026-08-29T22:42:52Z</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:33Z</t>
+          <t>2026-08-29T22:42:52Z</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:33Z</t>
+          <t>2026-08-29T22:42:52Z</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:33Z</t>
+          <t>2026-08-29T22:42:52Z</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T02:52:33Z</t>
+          <t>2026-08-29T22:42:52Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -7378,7 +7378,7 @@
       </c>
       <c r="L137" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:42:52Z</t>
+          <t>2026-08-30T22:52:30Z</t>
         </is>
       </c>
     </row>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:42:52Z</t>
+          <t>2026-08-30T22:52:30Z</t>
         </is>
       </c>
     </row>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="L139" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:42:52Z</t>
+          <t>2026-08-30T22:52:30Z</t>
         </is>
       </c>
     </row>
@@ -7534,7 +7534,7 @@
       </c>
       <c r="L140" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:42:52Z</t>
+          <t>2026-08-30T22:52:30Z</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>2026-08-29T22:42:52Z</t>
+          <t>2026-08-30T22:52:30Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L141"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7590,6 +7590,266 @@
         </is>
       </c>
     </row>
+    <row r="142">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="n">
+        <v>118.81265626</v>
+      </c>
+      <c r="E142" s="4" t="n"/>
+      <c r="F142" s="4" t="n"/>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H142" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I142" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J142" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L142" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C143" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="n">
+        <v>926.55312212</v>
+      </c>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H143" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I143" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K143" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L143" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="n">
+        <v>9.25863728</v>
+      </c>
+      <c r="E144" s="4" t="n"/>
+      <c r="F144" s="4" t="n"/>
+      <c r="G144" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H144" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I144" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L144" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="n">
+        <v>16.54335365</v>
+      </c>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H145" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I145" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L145" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:25Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B146" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="n">
+        <v>798.326</v>
+      </c>
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H146" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L146" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-31T23:58:25Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L146"/>
+  <dimension ref="A1:L151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7850,6 +7850,266 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="n">
+        <v>119.1852546</v>
+      </c>
+      <c r="E147" s="4" t="n"/>
+      <c r="F147" s="4" t="n"/>
+      <c r="G147" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H147" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I147" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K147" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L147" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:42:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B148" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="n">
+        <v>929.09083243</v>
+      </c>
+      <c r="E148" s="4" t="n"/>
+      <c r="F148" s="4" t="n"/>
+      <c r="G148" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H148" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I148" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K148" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L148" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:42:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="n">
+        <v>9.227737039999999</v>
+      </c>
+      <c r="E149" s="4" t="n"/>
+      <c r="F149" s="4" t="n"/>
+      <c r="G149" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H149" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K149" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L149" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:42:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B150" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="n">
+        <v>16.5976499</v>
+      </c>
+      <c r="E150" s="4" t="n"/>
+      <c r="F150" s="4" t="n"/>
+      <c r="G150" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H150" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I150" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J150" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K150" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L150" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:42:58Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="D151" s="5" t="n">
+        <v>801.1752</v>
+      </c>
+      <c r="E151" s="4" t="n"/>
+      <c r="F151" s="4" t="n"/>
+      <c r="G151" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H151" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I151" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J151" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K151" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L151" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-01T22:42:58Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L151"/>
+  <dimension ref="A1:L156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8110,6 +8110,266 @@
         </is>
       </c>
     </row>
+    <row r="152">
+      <c r="A152" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D152" s="5" t="n">
+        <v>119.79026568</v>
+      </c>
+      <c r="E152" s="4" t="n"/>
+      <c r="F152" s="4" t="n"/>
+      <c r="G152" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H152" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I152" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K152" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L152" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D153" s="5" t="n">
+        <v>932.80802553</v>
+      </c>
+      <c r="E153" s="4" t="n"/>
+      <c r="F153" s="4" t="n"/>
+      <c r="G153" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H153" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I153" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K153" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L153" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D154" s="5" t="n">
+        <v>9.22010409</v>
+      </c>
+      <c r="E154" s="4" t="n"/>
+      <c r="F154" s="4" t="n"/>
+      <c r="G154" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H154" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I154" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K154" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L154" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D155" s="5" t="n">
+        <v>16.66502876</v>
+      </c>
+      <c r="E155" s="4" t="n"/>
+      <c r="F155" s="4" t="n"/>
+      <c r="G155" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H155" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I155" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K155" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L155" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:20Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D156" s="5" t="n">
+        <v>804.8108999999999</v>
+      </c>
+      <c r="E156" s="4" t="n"/>
+      <c r="F156" s="4" t="n"/>
+      <c r="G156" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H156" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I156" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K156" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L156" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-02T22:45:20Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L156"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8370,6 +8370,266 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B157" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C157" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D157" s="5" t="n">
+        <v>120.18968083</v>
+      </c>
+      <c r="E157" s="4" t="n"/>
+      <c r="F157" s="4" t="n"/>
+      <c r="G157" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H157" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I157" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J157" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K157" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L157" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D158" s="5" t="n">
+        <v>938.44920184</v>
+      </c>
+      <c r="E158" s="4" t="n"/>
+      <c r="F158" s="4" t="n"/>
+      <c r="G158" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H158" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I158" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J158" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K158" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L158" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B159" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D159" s="5" t="n">
+        <v>9.318980270000001</v>
+      </c>
+      <c r="E159" s="4" t="n"/>
+      <c r="F159" s="4" t="n"/>
+      <c r="G159" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I159" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J159" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K159" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L159" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D160" s="5" t="n">
+        <v>16.71406332</v>
+      </c>
+      <c r="E160" s="4" t="n"/>
+      <c r="F160" s="4" t="n"/>
+      <c r="G160" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H160" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I160" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K160" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L160" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:28Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B161" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C161" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="D161" s="5" t="n">
+        <v>807.3862</v>
+      </c>
+      <c r="E161" s="4" t="n"/>
+      <c r="F161" s="4" t="n"/>
+      <c r="G161" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I161" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J161" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K161" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L161" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-03T22:43:28Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8630,6 +8630,266 @@
         </is>
       </c>
     </row>
+    <row r="162">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D162" s="5" t="n">
+        <v>121.26491714</v>
+      </c>
+      <c r="E162" s="4" t="n"/>
+      <c r="F162" s="4" t="n"/>
+      <c r="G162" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H162" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I162" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J162" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K162" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L162" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B163" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D163" s="5" t="n">
+        <v>945.65085917</v>
+      </c>
+      <c r="E163" s="4" t="n"/>
+      <c r="F163" s="4" t="n"/>
+      <c r="G163" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H163" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I163" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K163" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L163" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D164" s="5" t="n">
+        <v>9.47747612</v>
+      </c>
+      <c r="E164" s="4" t="n"/>
+      <c r="F164" s="4" t="n"/>
+      <c r="G164" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H164" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I164" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K164" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L164" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B165" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C165" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D165" s="5" t="n">
+        <v>16.79940088</v>
+      </c>
+      <c r="E165" s="4" t="n"/>
+      <c r="F165" s="4" t="n"/>
+      <c r="G165" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H165" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I165" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K165" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L165" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:30Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B166" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="D166" s="5" t="n">
+        <v>813.7361</v>
+      </c>
+      <c r="E166" s="4" t="n"/>
+      <c r="F166" s="4" t="n"/>
+      <c r="G166" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H166" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I166" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K166" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L166" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-04T22:26:30Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:30Z</t>
+          <t>2026-09-05T22:08:59Z</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:30Z</t>
+          <t>2026-09-05T22:08:59Z</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:30Z</t>
+          <t>2026-09-05T22:08:59Z</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:30Z</t>
+          <t>2026-09-05T22:08:59Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-04T22:26:30Z</t>
+          <t>2026-09-05T22:08:59Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -8678,7 +8678,7 @@
       </c>
       <c r="L162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:08:59Z</t>
+          <t>2026-09-06T22:12:12Z</t>
         </is>
       </c>
     </row>
@@ -8730,7 +8730,7 @@
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:08:59Z</t>
+          <t>2026-09-06T22:12:12Z</t>
         </is>
       </c>
     </row>
@@ -8782,7 +8782,7 @@
       </c>
       <c r="L164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:08:59Z</t>
+          <t>2026-09-06T22:12:12Z</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="L165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:08:59Z</t>
+          <t>2026-09-06T22:12:12Z</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-05T22:08:59Z</t>
+          <t>2026-09-06T22:12:12Z</t>
         </is>
       </c>
     </row>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L166"/>
+  <dimension ref="A1:L171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -8890,6 +8890,266 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B167" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D167" s="5" t="n">
+        <v>121.4089981</v>
+      </c>
+      <c r="E167" s="4" t="n"/>
+      <c r="F167" s="4" t="n"/>
+      <c r="G167" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H167" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I167" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K167" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L167" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B168" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D168" s="5" t="n">
+        <v>947.29802151</v>
+      </c>
+      <c r="E168" s="4" t="n"/>
+      <c r="F168" s="4" t="n"/>
+      <c r="G168" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H168" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I168" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K168" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L168" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C169" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D169" s="5" t="n">
+        <v>9.46195951</v>
+      </c>
+      <c r="E169" s="4" t="n"/>
+      <c r="F169" s="4" t="n"/>
+      <c r="G169" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H169" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I169" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K169" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L169" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D170" s="5" t="n">
+        <v>16.82279186</v>
+      </c>
+      <c r="E170" s="4" t="n"/>
+      <c r="F170" s="4" t="n"/>
+      <c r="G170" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H170" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I170" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J170" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K170" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L170" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:26Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="D171" s="5" t="n">
+        <v>814.6908</v>
+      </c>
+      <c r="E171" s="4" t="n"/>
+      <c r="F171" s="4" t="n"/>
+      <c r="G171" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H171" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I171" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J171" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K171" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L171" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07T22:56:26Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L171"/>
+  <dimension ref="A1:L176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9150,6 +9150,266 @@
         </is>
       </c>
     </row>
+    <row r="172">
+      <c r="A172" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D172" s="5" t="n">
+        <v>122.22083457</v>
+      </c>
+      <c r="E172" s="4" t="n"/>
+      <c r="F172" s="4" t="n"/>
+      <c r="G172" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H172" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I172" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J172" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K172" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L172" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D173" s="5" t="n">
+        <v>954.02442394</v>
+      </c>
+      <c r="E173" s="4" t="n"/>
+      <c r="F173" s="4" t="n"/>
+      <c r="G173" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H173" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I173" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J173" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K173" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L173" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D174" s="5" t="n">
+        <v>9.55255114</v>
+      </c>
+      <c r="E174" s="4" t="n"/>
+      <c r="F174" s="4" t="n"/>
+      <c r="G174" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H174" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I174" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K174" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L174" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D175" s="5" t="n">
+        <v>16.92501908</v>
+      </c>
+      <c r="E175" s="4" t="n"/>
+      <c r="F175" s="4" t="n"/>
+      <c r="G175" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H175" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I175" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K175" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L175" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:05Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D176" s="5" t="n">
+        <v>820.1018</v>
+      </c>
+      <c r="E176" s="4" t="n"/>
+      <c r="F176" s="4" t="n"/>
+      <c r="G176" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H176" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I176" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K176" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L176" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-08T22:51:05Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L176"/>
+  <dimension ref="A1:L181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9410,6 +9410,266 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D177" s="5" t="n">
+        <v>123.40103165</v>
+      </c>
+      <c r="E177" s="4" t="n"/>
+      <c r="F177" s="4" t="n"/>
+      <c r="G177" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H177" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I177" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J177" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K177" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L177" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D178" s="5" t="n">
+        <v>963.2128311500001</v>
+      </c>
+      <c r="E178" s="4" t="n"/>
+      <c r="F178" s="4" t="n"/>
+      <c r="G178" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H178" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I178" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K178" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L178" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D179" s="5" t="n">
+        <v>9.72803504</v>
+      </c>
+      <c r="E179" s="4" t="n"/>
+      <c r="F179" s="4" t="n"/>
+      <c r="G179" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I179" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K179" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L179" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D180" s="5" t="n">
+        <v>17.07653252</v>
+      </c>
+      <c r="E180" s="4" t="n"/>
+      <c r="F180" s="4" t="n"/>
+      <c r="G180" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H180" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I180" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J180" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K180" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L180" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:09Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="D181" s="5" t="n">
+        <v>827.7371000000001</v>
+      </c>
+      <c r="E181" s="4" t="n"/>
+      <c r="F181" s="4" t="n"/>
+      <c r="G181" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I181" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K181" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-09T22:40:09Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9670,6 +9670,266 @@
         </is>
       </c>
     </row>
+    <row r="182">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D182" s="5" t="n">
+        <v>124.14821939</v>
+      </c>
+      <c r="E182" s="4" t="n"/>
+      <c r="F182" s="4" t="n"/>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>968.06734453</v>
+      </c>
+      <c r="E183" s="4" t="n"/>
+      <c r="F183" s="4" t="n"/>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>9.91736367</v>
+      </c>
+      <c r="E184" s="4" t="n"/>
+      <c r="F184" s="4" t="n"/>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B185" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D185" s="5" t="n">
+        <v>17.16867194</v>
+      </c>
+      <c r="E185" s="4" t="n"/>
+      <c r="F185" s="4" t="n"/>
+      <c r="G185" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H185" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I185" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J185" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K185" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L185" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:12Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>832.4883</v>
+      </c>
+      <c r="E186" s="4" t="n"/>
+      <c r="F186" s="4" t="n"/>
+      <c r="G186" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H186" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I186" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J186" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K186" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L186" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-10T22:42:12Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L186"/>
+  <dimension ref="A1:L191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -9930,6 +9930,266 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_cny</t>
+        </is>
+      </c>
+      <c r="B187" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - CNY</t>
+        </is>
+      </c>
+      <c r="C187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>125.56193812</v>
+      </c>
+      <c r="E187" s="4" t="n"/>
+      <c r="F187" s="4" t="n"/>
+      <c r="G187" s="4" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="H187" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I187" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J187" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K187" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L187" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_eur</t>
+        </is>
+      </c>
+      <c r="B188" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - EUR</t>
+        </is>
+      </c>
+      <c r="C188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>977.8777773</v>
+      </c>
+      <c r="E188" s="4" t="n"/>
+      <c r="F188" s="4" t="n"/>
+      <c r="G188" s="4" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H188" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I188" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J188" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K188" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L188" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_rub</t>
+        </is>
+      </c>
+      <c r="B189" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - RUB</t>
+        </is>
+      </c>
+      <c r="C189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>10.01193172</v>
+      </c>
+      <c r="E189" s="4" t="n"/>
+      <c r="F189" s="4" t="n"/>
+      <c r="G189" s="4" t="inlineStr">
+        <is>
+          <t>RUB</t>
+        </is>
+      </c>
+      <c r="H189" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I189" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J189" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K189" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L189" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_try</t>
+        </is>
+      </c>
+      <c r="B190" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - TRY</t>
+        </is>
+      </c>
+      <c r="C190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>17.32921333</v>
+      </c>
+      <c r="E190" s="4" t="n"/>
+      <c r="F190" s="4" t="n"/>
+      <c r="G190" s="4" t="inlineStr">
+        <is>
+          <t>TRY</t>
+        </is>
+      </c>
+      <c r="H190" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I190" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J190" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K190" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L190" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:23Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>bcv_tipo_cambio_referencia_smc_usd</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>Tipo de Cambio de Referencia SMC - USD</t>
+        </is>
+      </c>
+      <c r="C191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>842.2067</v>
+      </c>
+      <c r="E191" s="4" t="n"/>
+      <c r="F191" s="4" t="n"/>
+      <c r="G191" s="4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="H191" s="4" t="inlineStr">
+        <is>
+          <t>VES por unidad de moneda extranjera</t>
+        </is>
+      </c>
+      <c r="I191" s="4" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="J191" s="4" t="inlineStr">
+        <is>
+          <t>Banco Central de Venezuela</t>
+        </is>
+      </c>
+      <c r="K191" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bcv.org.ve/estadisticas/tipo-cambio-de-referencia-smc</t>
+        </is>
+      </c>
+      <c r="L191" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-11T22:42:23Z</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
+++ b/assets/data/bcv/excel/ove_bcv_tipo_cambio_referencia_smc.xlsx
@@ -9978,7 +9978,7 @@
       </c>
       <c r="L187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:23Z</t>
+          <t>2026-09-12T22:26:43Z</t>
         </is>
       </c>
     </row>
@@ -10030,7 +10030,7 @@
       </c>
       <c r="L188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:23Z</t>
+          <t>2026-09-12T22:26:43Z</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10082,7 @@
       </c>
       <c r="L189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:23Z</t>
+          <t>2026-09-12T22:26:43Z</t>
         </is>
       </c>
     </row>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="L190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:23Z</t>
+          <t>2026-09-12T22:26:43Z</t>
         </is>
       </c>
     </row>
@@ -10186,7 +10186,7 @@
       </c>
       <c r="L191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-11T22:42:23Z</t>
+          <t>2026-09-12T22:26:43Z</t>
         </is>
       </c>
     </row>
